--- a/chapters/08/core/AIHE-B05/supp/AIHE-EX16/xlsx/AIHE-EX16_workbook.xlsx
+++ b/chapters/08/core/AIHE-B05/supp/AIHE-EX16/xlsx/AIHE-EX16_workbook.xlsx
@@ -84,12 +84,12 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
+      <alignment vertical="centre"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
+      <alignment vertical="centre"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -105,10 +105,10 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" wrapText="1"/>
+      <alignment horizontal="centre" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="centre" vertical="centre" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -116,10 +116,10 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" wrapText="1"/>
+      <alignment horizontal="centre" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="centre" vertical="centre" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
@@ -145,7 +145,7 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment vertical="centre" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -153,7 +153,7 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment vertical="centre" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
